--- a/data/Head Sold by Category & Quarter.xlsx
+++ b/data/Head Sold by Category & Quarter.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,46 +434,82 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Cows Under 5 MOS</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Cull Cows</t>
+          <t>Cows Over 2 Years</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Steers</t>
+          <t>Cows 5-24 MOS</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Q1</t>
-        </is>
+          <t>Jul-Sep '25</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>144</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q2</t>
-        </is>
+          <t>Oct-Dec '25</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>111</v>
+      </c>
+      <c r="C3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Q3</t>
-        </is>
+          <t>Jan-Mar '26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>130</v>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q4</t>
-        </is>
+          <t>Apr-Jun '26</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
